--- a/Unsorted/Петергоф/восстановление/петергоф_восстановление_подписи.xlsx
+++ b/Unsorted/Петергоф/восстановление/петергоф_восстановление_подписи.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23232" windowHeight="13152" tabRatio="949" firstSheet="33" activeTab="52"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23232" windowHeight="13152" tabRatio="949" firstSheet="29" activeTab="37"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,8 +41,8 @@
     <sheet name="Лист4" sheetId="47" r:id="rId32"/>
     <sheet name="Лист12" sheetId="55" r:id="rId33"/>
     <sheet name="Лист13" sheetId="56" r:id="rId34"/>
-    <sheet name="Лист14" sheetId="57" r:id="rId35"/>
-    <sheet name="Лист15" sheetId="58" r:id="rId36"/>
+    <sheet name="Лист15" sheetId="58" r:id="rId35"/>
+    <sheet name="Лист14" sheetId="57" r:id="rId36"/>
     <sheet name="Лист16" sheetId="59" r:id="rId37"/>
     <sheet name="Лист17" sheetId="60" r:id="rId38"/>
     <sheet name="Sheet16" sheetId="16" r:id="rId39"/>
@@ -2857,7 +2857,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5436,10 +5436,10 @@
     </row>
     <row r="4" spans="1:2" ht="57.6">
       <c r="A4" s="2" t="s">
-        <v>481</v>
+        <v>384</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>480</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -5479,10 +5479,10 @@
     </row>
     <row r="4" spans="1:2" ht="57.6">
       <c r="A4" s="2" t="s">
-        <v>384</v>
+        <v>481</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>383</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
